--- a/fase2/Evidencias Proyecto/Evidencias de Documentacion/03_Sprint_Backlog/Sprint_03/DPAY3_Sprint_Backlog_S03.xlsx
+++ b/fase2/Evidencias Proyecto/Evidencias de Documentacion/03_Sprint_Backlog/Sprint_03/DPAY3_Sprint_Backlog_S03.xlsx
@@ -530,7 +530,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sprint Backlog — D-PAY 3.0 — Sprint 3 (Semanas 9 y 10, 06/10/2026 – 19/10/2026)</t>
+          <t>Sprint Backlog - D-PAY 3.0 - Sprint 3 (Semanas 9 y 10, 06/10/2026 – 19/10/2026)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -539,6 +539,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1072,6 +1073,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
